--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-DICOMExpositionRadiations.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-DICOMExpositionRadiations.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="114">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-27T14:36:02+00:00</t>
+    <t>2025-06-05T15:38:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -292,60 +292,76 @@
     <t>DICOMExpositionRadiations.sousSection</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Section
-</t>
-  </si>
-  <si>
-    <t>Sous-sections</t>
-  </si>
-  <si>
-    <t>Section.sousSection</t>
-  </si>
-  <si>
-    <t>DICOMExpositionRadiations.entree</t>
-  </si>
-  <si>
     <t xml:space="preserve">Base
 </t>
   </si>
   <si>
+    <t>Sous-sections</t>
+  </si>
+  <si>
+    <t>Section.sousSection</t>
+  </si>
+  <si>
+    <t>DICOMExpositionRadiations.entree</t>
+  </si>
+  <si>
     <t>Entrées</t>
   </si>
   <si>
     <t>Section.entree</t>
   </si>
   <si>
-    <t>DICOMExpositionRadiations.sOPInstanceObservation</t>
+    <t>DICOMExpositionRadiations.entree.sOPInstanceObservation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/DICOMSOPInstanceObservation
+</t>
   </si>
   <si>
     <t>Entrée SOP instance Observation</t>
   </si>
   <si>
-    <t>DICOMExpositionRadiations.expositionRayonnements</t>
+    <t>DICOMExpositionRadiations.entree.expositionRayonnements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/DICOMExpositionPatient
+</t>
   </si>
   <si>
     <t>Entrée Exposition aux rayonnements ionisants</t>
   </si>
   <si>
-    <t>DICOMExpositionRadiations.observationGrossesse</t>
+    <t>DICOMExpositionRadiations.entree.observationGrossesse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/DICOMObservation
+</t>
   </si>
   <si>
     <t>Entrée Observation Grossesse</t>
   </si>
   <si>
-    <t>DICOMExpositionRadiations.observationIndication</t>
+    <t>DICOMExpositionRadiations.entree.observationIndication</t>
   </si>
   <si>
     <t>Entrée Observation Indication</t>
   </si>
   <si>
-    <t>DICOMExpositionRadiations.quantite</t>
+    <t>DICOMExpositionRadiations.entree.quantite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/DICOMQuantity
+</t>
   </si>
   <si>
     <t>Entrée Quantité</t>
   </si>
   <si>
-    <t>DICOMExpositionRadiations.administrationRadiopharmaceutique</t>
+    <t>DICOMExpositionRadiations.entree.administrationRadiopharmaceutique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/DICOMAdministrationProduitDeSante
+</t>
   </si>
   <si>
     <t>Entrée Administration des produits radiopharmaceutiques</t>
@@ -653,8 +669,8 @@
   <dimension ref="A1:AJ13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.99609375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="51.99609375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="57.65625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="57.65625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -663,7 +679,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="60.3125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="83.68359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -684,7 +700,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="51.99609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="57.65625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1216,7 +1232,7 @@
         <v>73</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>72</v>
@@ -1328,13 +1344,13 @@
         <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L7" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="M7" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1385,7 +1401,7 @@
         <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>73</v>
@@ -1402,10 +1418,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1428,7 +1444,7 @@
         <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L8" t="s" s="2">
         <v>99</v>
@@ -1485,7 +1501,7 @@
         <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>73</v>
@@ -1528,13 +1544,13 @@
         <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1602,10 +1618,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1628,13 +1644,13 @@
         <v>72</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1685,7 +1701,7 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -1702,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1728,13 +1744,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1785,7 +1801,7 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>73</v>
@@ -1802,10 +1818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1828,13 +1844,13 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1885,7 +1901,7 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>73</v>
@@ -1902,10 +1918,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -1928,13 +1944,13 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -1985,7 +2001,7 @@
         <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>73</v>

--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-DICOMExpositionRadiations.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-DICOMExpositionRadiations.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-05T15:38:56+00:00</t>
+    <t>2025-10-06T12:29:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
